--- a/InputData/endo-learn/PDiBCpDoC/Perc Decline in Battery Cost per Doubling of Cap.xlsx
+++ b/InputData/endo-learn/PDiBCpDoC/Perc Decline in Battery Cost per Doubling of Cap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\endo-learn\PDiBCpDoC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D81FD32-760B-4369-A9B7-97CB22806FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7390D6EA-97F6-4AA3-ACAE-4B5301F6F025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Source:</t>
   </si>
@@ -46,19 +46,13 @@
     <t>Perc Decline per Doubling (dimensionless)</t>
   </si>
   <si>
-    <t>https://pubs.rsc.org/en/content/articlepdf/2021/ee/d0ee02681f?page=search</t>
-  </si>
-  <si>
-    <t>Re-examining rates of lithium-ion battery technology improvement and cost decline</t>
-  </si>
-  <si>
-    <t>Massachusetts Institute of Technology</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Note: We take the average of learning rates quoted in the Abstract (20%-27%)</t>
+    <t>BNEF</t>
+  </si>
+  <si>
+    <t>A Behind the Scenes Take on Lithium-ion Battery Prices</t>
+  </si>
+  <si>
+    <t>https://about.bnef.com/blog/behind-scenes-take-lithium-ion-battery-prices/</t>
   </si>
 </sst>
 </file>
@@ -110,13 +104,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -135,9 +130,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,9 +170,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -210,26 +205,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -262,26 +240,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -455,49 +416,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -511,23 +465,22 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <f>AVERAGE(0.2,0.27)</f>
-        <v>0.23500000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
